--- a/data/trans_dic/IP2003-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen dientes o muelas empastados</t>
+          <t>Menores que tienen dientes o muelas empastados (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,33</t>
+          <t>0,0; 12,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 5,78</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,14</t>
+          <t>2,73; 7,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,07</t>
+          <t>2,53; 7,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,11</t>
+          <t>3,36; 8,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 10,44</t>
+          <t>3,96; 10,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,83</t>
+          <t>2,58; 6,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,75</t>
+          <t>3,5; 8,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 7,17</t>
+          <t>2,42; 7,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,64</t>
+          <t>3,84; 10,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,05</t>
+          <t>2,98; 6,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,96</t>
+          <t>3,66; 6,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,73</t>
+          <t>3,59; 7,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 9,32</t>
+          <t>4,56; 9,03</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,68; 34,64</t>
+          <t>21,64; 34,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,57; 34,8</t>
+          <t>22,74; 34,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,27; 22,45</t>
+          <t>13,9; 23,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,58; 24,52</t>
+          <t>12,3; 24,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,33; 27,71</t>
+          <t>16,37; 28,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,2; 25,2</t>
+          <t>15,27; 25,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,17; 24,77</t>
+          <t>14,92; 23,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 16,55</t>
+          <t>7,81; 16,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,22; 28,65</t>
+          <t>20,59; 28,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,42; 27,83</t>
+          <t>20,24; 28,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,22; 22,13</t>
+          <t>15,66; 22,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,83; 17,86</t>
+          <t>11,28; 18,3</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,9; 39,35</t>
+          <t>29,52; 40,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,52; 39,1</t>
+          <t>26,99; 39,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,21; 31,55</t>
+          <t>20,29; 31,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,9; 49,08</t>
+          <t>17,12; 48,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,71; 32,16</t>
+          <t>22,4; 32,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,68; 30,92</t>
+          <t>21,06; 31,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 29,8</t>
+          <t>19,26; 30,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,83; 32,09</t>
+          <t>16,49; 31,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,72; 34,4</t>
+          <t>27,25; 34,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,27; 33,32</t>
+          <t>25,41; 33,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,38; 29,43</t>
+          <t>21,05; 28,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,4; 36,31</t>
+          <t>18,7; 38,02</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,19; 19,93</t>
+          <t>15,33; 20,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,38; 19,21</t>
+          <t>14,54; 19,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,24; 15,73</t>
+          <t>11,29; 15,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,76; 28,55</t>
+          <t>12,71; 29,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,22; 16,33</t>
+          <t>12,35; 16,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,44</t>
+          <t>11,25; 15,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 15,14</t>
+          <t>11,14; 15,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,46; 18,73</t>
+          <t>11,39; 18,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,28; 17,45</t>
+          <t>14,33; 17,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,3; 16,49</t>
+          <t>13,37; 16,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,75; 14,83</t>
+          <t>11,82; 14,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,05; 21,88</t>
+          <t>12,91; 21,3</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen dientes o muelas empastados (tasa de respuesta: 99,85%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6159</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5567</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11288</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10823</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11888</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10612</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10735</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14840</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11627</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>11983</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>22023</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>25663</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>23515</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>22595</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6887; 18169</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5966; 17276</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7049; 18179</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6304; 17203</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6536; 16832</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>9417; 22341</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6233; 18181</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>6976; 19000</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>15076; 30406</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>18476; 35295</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>16799; 33798</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>15538; 30779</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>35135</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43766</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33428</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30227</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>30533</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31754</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>36439</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>24905</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>65668</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>75519</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>69867</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>55133</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>27602; 44428</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35707; 53408</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26250; 44263</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21281; 41800</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23037; 39480</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>24218; 40375</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>28132; 45173</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>16604; 35331</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>55232; 77758</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>63873; 88407</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>59120; 83512</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>43473; 70574</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>66882</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>56642</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>43639</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>72209</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>56267</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>46203</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>42836</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>67359</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>123149</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>102846</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>86474</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>139568</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>57291; 77860</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>46074; 66973</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>34889; 53488</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>47160; 133316</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>46153; 67080</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>37902; 55899</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>33526; 53313</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>50383; 97030</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>109047; 138462</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>89125; 117184</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>72845; 99387</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>108661; 220863</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>113305</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>111231</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>88955</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>113048</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97535</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92797</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90901</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>105364</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>210840</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>204028</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>179856</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>218412</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>98898; 129850</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>96409; 127193</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>74365; 103934</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>83378; 192532</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>84568; 112638</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>79135; 109947</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>78067; 107974</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>85121; 138824</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>190643; 232740</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>182712; 225701</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>160639; 202155</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>181128; 298933</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2003-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Edad-trans_dic.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,85</t>
+          <t>0,0; 9,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,19</t>
+          <t>2,64; 6,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,31</t>
+          <t>2,5; 7,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 8,66</t>
+          <t>3,4; 8,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 10,81</t>
+          <t>3,89; 10,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,65</t>
+          <t>2,6; 6,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 8,31</t>
+          <t>3,45; 8,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,05</t>
+          <t>2,58; 6,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 10,46</t>
+          <t>3,84; 10,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,01</t>
+          <t>3,22; 6,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,99</t>
+          <t>3,56; 7,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,22</t>
+          <t>3,62; 7,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 9,03</t>
+          <t>4,47; 9,23</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,64; 34,83</t>
+          <t>21,04; 33,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,74; 34,01</t>
+          <t>22,2; 34,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,9; 23,43</t>
+          <t>13,73; 22,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,3; 24,15</t>
+          <t>12,8; 24,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,37; 28,06</t>
+          <t>16,74; 27,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,27; 25,46</t>
+          <t>15,2; 25,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,92; 23,96</t>
+          <t>15,01; 24,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,81; 16,63</t>
+          <t>8,12; 16,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,59; 28,99</t>
+          <t>20,48; 29,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,24; 28,01</t>
+          <t>20,36; 27,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,66; 22,12</t>
+          <t>15,16; 21,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,28; 18,3</t>
+          <t>11,21; 18,42</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,52; 40,11</t>
+          <t>28,91; 39,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,99; 39,23</t>
+          <t>27,6; 39,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,29; 31,1</t>
+          <t>20,61; 32,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,12; 48,4</t>
+          <t>16,73; 49,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,4; 32,56</t>
+          <t>22,82; 32,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,06; 31,06</t>
+          <t>20,63; 31,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,26; 30,63</t>
+          <t>19,22; 30,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,49; 31,76</t>
+          <t>16,39; 32,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,25; 34,6</t>
+          <t>27,21; 34,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,41; 33,42</t>
+          <t>25,4; 33,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,05; 28,72</t>
+          <t>21,27; 29,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,7; 38,02</t>
+          <t>18,33; 36,48</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,33; 20,13</t>
+          <t>15,26; 20,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,54; 19,19</t>
+          <t>14,58; 19,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,78</t>
+          <t>11,23; 15,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,71; 29,35</t>
+          <t>12,97; 29,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,35; 16,45</t>
+          <t>12,25; 16,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,63</t>
+          <t>11,34; 15,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,14; 15,41</t>
+          <t>11,07; 15,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,39; 18,57</t>
+          <t>11,3; 19,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,33; 17,5</t>
+          <t>14,33; 17,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,37; 16,52</t>
+          <t>13,36; 16,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,82; 14,87</t>
+          <t>11,67; 14,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,91; 21,3</t>
+          <t>12,88; 21,61</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6159</t>
+          <t>0; 4614</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5567</t>
+          <t>0; 6135</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6887; 18169</t>
+          <t>6672; 16774</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5966; 17276</t>
+          <t>5918; 17491</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7049; 18179</t>
+          <t>7128; 18343</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6304; 17203</t>
+          <t>6187; 16857</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6536; 16832</t>
+          <t>6578; 16800</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9417; 22341</t>
+          <t>9286; 22342</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6233; 18181</t>
+          <t>6668; 17964</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6976; 19000</t>
+          <t>6971; 19292</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15076; 30406</t>
+          <t>16304; 31318</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18476; 35295</t>
+          <t>18009; 36339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16799; 33798</t>
+          <t>16919; 32875</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15538; 30779</t>
+          <t>15213; 31449</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27602; 44428</t>
+          <t>26832; 43160</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35707; 53408</t>
+          <t>34866; 54033</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26250; 44263</t>
+          <t>25932; 42216</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21281; 41800</t>
+          <t>22153; 42786</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23037; 39480</t>
+          <t>23548; 39141</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24218; 40375</t>
+          <t>24096; 40511</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28132; 45173</t>
+          <t>28304; 46187</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16604; 35331</t>
+          <t>17261; 35360</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55232; 77758</t>
+          <t>54938; 78289</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63873; 88407</t>
+          <t>64271; 87134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59120; 83512</t>
+          <t>57234; 82565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43473; 70574</t>
+          <t>43235; 71012</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57291; 77860</t>
+          <t>56113; 77588</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46074; 66973</t>
+          <t>47116; 66631</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34889; 53488</t>
+          <t>35440; 55321</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47160; 133316</t>
+          <t>46097; 135755</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46153; 67080</t>
+          <t>47014; 66720</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37902; 55899</t>
+          <t>37124; 56041</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33526; 53313</t>
+          <t>33454; 52888</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50383; 97030</t>
+          <t>50057; 99170</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>109047; 138462</t>
+          <t>108881; 137613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>89125; 117184</t>
+          <t>89090; 117439</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72845; 99387</t>
+          <t>73582; 101414</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>108661; 220863</t>
+          <t>106503; 211929</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>98898; 129850</t>
+          <t>98461; 130729</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96409; 127193</t>
+          <t>96632; 128679</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74365; 103934</t>
+          <t>73987; 105283</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83378; 192532</t>
+          <t>85095; 196712</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>84568; 112638</t>
+          <t>83875; 112949</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79135; 109947</t>
+          <t>79780; 109427</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78067; 107974</t>
+          <t>77560; 108202</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>85121; 138824</t>
+          <t>84499; 142608</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>190643; 232740</t>
+          <t>190555; 231108</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182712; 225701</t>
+          <t>182534; 225112</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>160639; 202155</t>
+          <t>158663; 200926</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>181128; 298933</t>
+          <t>180719; 303305</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2003-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -664,29 +664,29 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -732,29 +732,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,06</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,63</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,47%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,58%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,67%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,64</t>
+          <t>2,59; 6,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,4</t>
+          <t>3,57; 8,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 8,74</t>
+          <t>2,49; 7,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 10,59</t>
+          <t>3,95; 10,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,64</t>
+          <t>2,83; 7,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,31</t>
+          <t>2,57; 7,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,96</t>
+          <t>3,37; 9,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 10,63</t>
+          <t>4,08; 11,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,19</t>
+          <t>3,12; 6,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,19</t>
+          <t>3,66; 6,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,03</t>
+          <t>3,53; 6,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 9,23</t>
+          <t>4,8; 9,85</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21,7%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20,02%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10,96%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>27,55%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>27,87%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>17,7%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,32%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,04; 33,84</t>
+          <t>16,33; 27,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,2; 34,41</t>
+          <t>15,2; 25,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,73; 22,35</t>
+          <t>15,17; 24,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,8; 24,72</t>
+          <t>7,01; 15,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,74; 27,82</t>
+          <t>21,68; 34,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,2; 25,55</t>
+          <t>22,57; 34,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,01; 24,49</t>
+          <t>13,27; 22,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 16,64</t>
+          <t>11,47; 21,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,48; 29,19</t>
+          <t>20,22; 28,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,36; 27,61</t>
+          <t>20,42; 27,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,16; 21,87</t>
+          <t>15,22; 22,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,21; 18,42</t>
+          <t>10,23; 16,58</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25,67%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24,61%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21,22%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>34,46%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>33,18%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>25,38%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26,21%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,61%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,91; 39,97</t>
+          <t>22,71; 32,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,6; 39,03</t>
+          <t>20,68; 30,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,61; 32,17</t>
+          <t>19,07; 29,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,73; 49,28</t>
+          <t>16,49; 30,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,82; 32,38</t>
+          <t>28,9; 39,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,63; 31,14</t>
+          <t>27,52; 39,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,22; 30,39</t>
+          <t>20,21; 31,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 32,46</t>
+          <t>15,11; 24,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,21; 34,39</t>
+          <t>26,72; 34,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,4; 33,49</t>
+          <t>25,27; 33,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,27; 29,31</t>
+          <t>21,38; 29,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,33; 36,48</t>
+          <t>16,77; 25,26</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>17,57%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>16,78%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>13,51%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,26; 20,27</t>
+          <t>12,22; 16,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 19,41</t>
+          <t>11,29; 15,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,23; 15,99</t>
+          <t>11,05; 15,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,97; 29,98</t>
+          <t>11,22; 18,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 16,49</t>
+          <t>15,19; 19,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,34; 15,56</t>
+          <t>14,38; 19,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,07; 15,44</t>
+          <t>11,24; 15,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,3; 19,08</t>
+          <t>11,91; 16,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,33; 17,38</t>
+          <t>14,28; 17,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,36; 16,48</t>
+          <t>13,3; 16,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,67; 14,78</t>
+          <t>11,75; 14,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,88; 21,61</t>
+          <t>12,21; 16,31</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1592,29 +1592,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>392</t>
         </is>
       </c>
     </row>
@@ -1660,29 +1660,29 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 2008</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4614</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 6135</t>
+          <t>0; 1936</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10735</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14840</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11627</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10485</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11288</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10823</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11888</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10612</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10735</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14840</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11627</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22595</t>
+          <t>20976</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6672; 16774</t>
+          <t>6561; 17287</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5918; 17491</t>
+          <t>9599; 23534</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7128; 18343</t>
+          <t>6438; 18504</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6187; 16857</t>
+          <t>6193; 16939</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6578; 16800</t>
+          <t>7151; 18040</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9286; 22342</t>
+          <t>6078; 16707</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6668; 17964</t>
+          <t>7066; 19113</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6971; 19292</t>
+          <t>5913; 16982</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16304; 31318</t>
+          <t>15756; 30593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18009; 36339</t>
+          <t>18493; 35145</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16919; 32875</t>
+          <t>16517; 31508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15213; 31449</t>
+          <t>14478; 29721</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>30533</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31754</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>36439</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21935</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>35135</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>43766</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>33428</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30227</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>30533</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31754</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>36439</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24905</t>
+          <t>28093</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55133</t>
+          <t>50028</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26832; 43160</t>
+          <t>22975; 38989</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34866; 54033</t>
+          <t>24101; 39957</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25932; 42216</t>
+          <t>28615; 46701</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22153; 42786</t>
+          <t>14026; 30856</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23548; 39141</t>
+          <t>27658; 44179</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24096; 40511</t>
+          <t>35447; 54652</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28304; 46187</t>
+          <t>25064; 42399</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17261; 35360</t>
+          <t>20028; 37579</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>54938; 78289</t>
+          <t>54251; 76849</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64271; 87134</t>
+          <t>64438; 87841</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57234; 82565</t>
+          <t>57435; 83539</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43235; 71012</t>
+          <t>38359; 62157</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>56267</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46203</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42836</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>62099</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>66882</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>56642</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>43639</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>72209</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>56267</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>46203</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>42836</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>67359</t>
+          <t>48996</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>139568</t>
+          <t>111095</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>56113; 77588</t>
+          <t>46791; 66269</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47116; 66631</t>
+          <t>37214; 55646</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35440; 55321</t>
+          <t>33184; 51869</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46097; 135755</t>
+          <t>48257; 87827</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47014; 66720</t>
+          <t>56085; 76383</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37124; 56041</t>
+          <t>46988; 66758</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33454; 52888</t>
+          <t>34763; 54257</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50057; 99170</t>
+          <t>38773; 61776</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>108881; 137613</t>
+          <t>106930; 137650</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>89090; 117439</t>
+          <t>88629; 116832</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73582; 101414</t>
+          <t>73980; 101822</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>106503; 211929</t>
+          <t>92102; 138749</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>120</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>97535</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>92797</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>90901</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>94910</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>113305</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>111231</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>88955</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>113048</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97535</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92797</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>90901</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>105364</t>
+          <t>87580</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>218412</t>
+          <t>182490</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>98461; 130729</t>
+          <t>83687; 111819</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96632; 128679</t>
+          <t>79432; 108594</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73987; 105283</t>
+          <t>77447; 106142</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85095; 196712</t>
+          <t>77347; 124939</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>83875; 112949</t>
+          <t>97996; 128552</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79780; 109427</t>
+          <t>95300; 127320</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77560; 108202</t>
+          <t>73998; 103586</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>84499; 142608</t>
+          <t>73954; 103379</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>190555; 231108</t>
+          <t>189962; 232012</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182534; 225112</t>
+          <t>181667; 225261</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158663; 200926</t>
+          <t>159691; 201619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>180719; 303305</t>
+          <t>159899; 213725</t>
         </is>
       </c>
     </row>
